--- a/facility_management_forms/006_vision_and_lighting_assessment_form--facility_management_forms.xlsx
+++ b/facility_management_forms/006_vision_and_lighting_assessment_form--facility_management_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,23 +515,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>facility_id</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>facility_id</t>
+          <t>What is your position in the organization?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,41 +543,41 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>facility_name</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>What is the name of your facility?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>area_id</t>
+          <t>lighting_condition</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>area_id</t>
+          <t>What is the overall condition of the lighting at your facility?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,18 +589,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>lighting_condition_id</t>
+          <t>lighting_level</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>lighting_condition_id</t>
+          <t>What is the current lighting level at your facility?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,64 +612,64 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>lighting_level_id</t>
+          <t>lighting_intensity</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>lighting_level_id</t>
+          <t>What is the intensity of the lighting at your facility?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>lighting_intensity_id</t>
+          <t>observations</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>lighting_intensity_id</t>
+          <t>Please note any observations about the lighting conditions at your facility</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>lighting_characteristics</t>
+          <t>issue_reported</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>lighting_characteristics</t>
+          <t>If there is an issue with the lighting, please report it</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,87 +681,87 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>observations</t>
+          <t>next_action</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>observations</t>
+          <t>What action will be taken to address the issue?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>issue_reported</t>
+          <t>next_action_date</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>issue_reported</t>
+          <t>What is the next action due date?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>action_taken</t>
+          <t>follow_up_status</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>action_taken</t>
+          <t>What is the status of the follow-up?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>next_action_due</t>
+          <t>follow_up_frequency</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>next_action_due</t>
+          <t>What is the follow-up frequency?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -773,317 +773,41 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>next_action_by</t>
+          <t>follow_up_method</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>next_action_by</t>
+          <t>How will the follow-up be conducted?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>action_status</t>
+          <t>follow_up_comments</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>action_status</t>
+          <t>Please enter any follow-up comments</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>follow_up</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>follow_up</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>follow_up_by</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>follow_up_by</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>follow_up_date</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>follow_up_date</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>follow_up_by</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>follow_up_by</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>follow_up_status</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>follow_up_status</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>follow_up_comments</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>follow_up_comments</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>facility_manager_id</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>facility_manager_id</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>follow_up_frequency</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>follow_up_frequency</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>follow_up_method</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>follow_up_method</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>follow_up_status</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>follow_up_status</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>follow_up_comments</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>follow_up_comments</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,10 +822,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C45"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1126,748 +850,221 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>facility_id_choices</t>
+          <t>lighting_level_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>facilities_1</t>
+          <t>adequate</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Facilities 1</t>
+          <t>Adequate</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>facility_id_choices</t>
+          <t>lighting_level_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>facilities_2</t>
+          <t>inadequate</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Facilities 2</t>
+          <t>Inadequate</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>area_id_choices</t>
+          <t>lighting_intensity_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>area_1</t>
+          <t>sufficient</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Area 1</t>
+          <t>Sufficient</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>area_id_choices</t>
+          <t>lighting_intensity_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>area_2</t>
+          <t>insufficient</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Area 2</t>
+          <t>Insufficient</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>area_id_choices</t>
+          <t>follow_up_status_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>area_3</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Area 3</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>lighting_condition_id_choices</t>
+          <t>follow_up_status_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>condition_1</t>
+          <t>ongoing</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Condition 1</t>
+          <t>Ongoing</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>lighting_condition_id_choices</t>
+          <t>follow_up_status_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>condition_2</t>
+          <t>scheduled</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Condition 2</t>
+          <t>Scheduled</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>lighting_condition_id_choices</t>
+          <t>follow_up_frequency_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>condition_3</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Condition 3</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>lighting_level_id_choices</t>
+          <t>follow_up_frequency_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>level_1</t>
+          <t>bi-weekly</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Level 1</t>
+          <t>Bi-Weekly</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>lighting_level_id_choices</t>
+          <t>follow_up_frequency_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>level_2</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>lighting_level_id_choices</t>
+          <t>follow_up_method_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>level_3</t>
+          <t>phone_call</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Phone Call</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>lighting_intensity_id_choices</t>
+          <t>follow_up_method_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>intensity_1</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Intensity 1</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>lighting_intensity_id_choices</t>
+          <t>follow_up_method_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>intensity_2</t>
+          <t>meeting</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Intensity 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>lighting_intensity_id_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>intensity_3</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Intensity 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>next_action_by_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>user_1</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>User 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>next_action_by_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>user_2</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>User 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>next_action_by_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>user_3</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>User 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>action_status_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>status_1</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Status 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>action_status_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>status_2</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Status 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>action_status_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>status_3</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Status 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>follow_up_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>follow-up_1</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Follow-up 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>follow_up_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>follow-up_2</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Follow-up 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>follow_up_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>follow-up_3</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Follow-up 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>follow_up_by_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>follow-up_1</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Follow-up 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>follow_up_by_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>follow-up_2</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Follow-up 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>follow_up_by_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>follow-up_3</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Follow-up 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>follow_up_by_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>follow-up_1</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Follow-up 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>follow_up_by_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>follow-up_2</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Follow-up 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>follow_up_by_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>follow-up_3</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Follow-up 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>follow_up_status_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>status_1</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Status 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>follow_up_status_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>status_2</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Status 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>follow_up_status_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>status_3</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Status 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>facility_manager_id_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>manager_1</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Manager 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>facility_manager_id_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>manager_2</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Manager 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>facility_manager_id_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>manager_3</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Manager 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>follow_up_frequency_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>frequency_1</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Frequency 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>follow_up_frequency_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>frequency_2</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Frequency 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>follow_up_frequency_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>frequency_3</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Frequency 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>follow_up_method_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>method_1</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Method 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>follow_up_method_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>method_2</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Method 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>follow_up_method_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>method_3</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Method 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>follow_up_status_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>status_1</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Status 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>follow_up_status_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>status_2</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Status 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>follow_up_status_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>status_3</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Status 3</t>
+          <t>Meeting</t>
         </is>
       </c>
     </row>
